--- a/example_coder.xlsx
+++ b/example_coder.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,21 +536,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0aedb90b-acb4-497a-a324-c1c8c6f0633a</t>
+          <t>03adb252-86b1-4e38-8124-e373ab1bfe04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wallis Orchard MAY 2026 SUNDAY USPSA Match</t>
+          <t>Brazosland Pistoleros USPSA- SUNDAY August 9th</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -559,18 +559,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.67%</t>
+          <t>72.74%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>580.3988000000001</v>
+        <v>451.9354</v>
       </c>
       <c r="H2" t="n">
-        <v>121.96</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>87.95%</t>
+          <t>64.56%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -589,49 +589,47 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>A170259</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="P2" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0aedb90b-acb4-497a-a324-c1c8c6f0633a.csv</t>
+          <t>03adb252-86b1-4e38-8124-e373ab1bfe04.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1a211aed-8fcd-440b-98aa-a19053327049</t>
+          <t>0aedb90b-acb4-497a-a324-c1c8c6f0633a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wallis Orchard Sep 2026 USPSA Match</t>
+          <t>Wallis Orchard MAY 2026 SUNDAY USPSA Match</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -640,18 +638,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73.03%</t>
+          <t>76.67%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>580.3680000000001</v>
+        <v>580.3988000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>106.26</v>
+        <v>121.96</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>68.68%</t>
+          <t>87.95%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -661,7 +659,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -676,45 +674,43 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="P3" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1a211aed-8fcd-440b-98aa-a19053327049.csv</t>
+          <t>0aedb90b-acb4-497a-a324-c1c8c6f0633a.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1cde22e7-3137-4bd7-babb-f5a32669dc97</t>
+          <t>161d6ac4-d5a0-46bb-b615-ae39a0dd5a8d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Baps USPSA October 2025</t>
+          <t>GPS USPSA September 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -723,18 +719,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.71%</t>
+          <t>79.54%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>485.5537</v>
+        <v>571.9902</v>
       </c>
       <c r="H4" t="n">
-        <v>103.62</v>
+        <v>90.78</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>82.15%</t>
+          <t>73.81%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -744,7 +740,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -759,67 +755,65 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="P4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1cde22e7-3137-4bd7-babb-f5a32669dc97.csv</t>
+          <t>161d6ac4-d5a0-46bb-b615-ae39a0dd5a8d.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1d8d66d7-2c97-4f42-8849-7283c7cfeb59</t>
+          <t>1a211aed-8fcd-440b-98aa-a19053327049</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPS USPSA June 2026</t>
+          <t>Wallis Orchard Sep 2026 USPSA Match</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>73.03%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>535.8953</v>
+        <v>580.3680000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>108.64</v>
+        <v>106.26</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>88.87%</t>
+          <t>68.68%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -829,7 +823,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -840,17 +834,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="P5" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
@@ -861,28 +855,28 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1d8d66d7-2c97-4f42-8849-7283c7cfeb59.csv</t>
+          <t>1a211aed-8fcd-440b-98aa-a19053327049.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2c827641-7121-4f91-b9b6-8d643d7a16cc</t>
+          <t>1cde22e7-3137-4bd7-babb-f5a32669dc97</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPS USPSA November 2025</t>
+          <t>Baps USPSA October 2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -891,18 +885,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.68%</t>
+          <t>66.71%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>371.2574</v>
+        <v>485.5537</v>
       </c>
       <c r="H6" t="n">
-        <v>150.81</v>
+        <v>103.62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>74.71%</t>
+          <t>82.15%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -912,7 +906,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -927,69 +921,67 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="P6" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
         <v>1</v>
       </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2c827641-7121-4f91-b9b6-8d643d7a16cc.csv</t>
+          <t>1cde22e7-3137-4bd7-babb-f5a32669dc97.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2df6136a-9469-480b-a2c6-e45719ab0472</t>
+          <t>1d8d66d7-2c97-4f42-8849-7283c7cfeb59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPS USPSA November Extra Saturday 2025</t>
+          <t>GPS USPSA June 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.48%</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>452.7645</v>
+        <v>535.8953</v>
       </c>
       <c r="H7" t="n">
-        <v>147.81</v>
+        <v>108.64</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.04%</t>
+          <t>88.87%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -999,7 +991,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1010,71 +1002,67 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>A170259</t>
+          <t>A178525</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="P7" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2df6136a-9469-480b-a2c6-e45719ab0472.csv</t>
+          <t>1d8d66d7-2c97-4f42-8849-7283c7cfeb59.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31f98761-4e09-4aa9-b656-e134cc8c4929</t>
+          <t>2234b6eb-d6fb-46fc-ae5a-8116e1345c28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPS USPSA August 2025</t>
+          <t>Kidlat Shooters AUGUST USPSA match 08-01-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>398.7853</v>
-      </c>
-      <c r="H8" t="n">
-        <v>159.34</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85.67%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1084,7 +1072,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1095,15 +1083,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A170259</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>117</v>
-      </c>
-      <c r="P8" t="n">
-        <v>28</v>
-      </c>
+          <t>A178525</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -1112,48 +1096,48 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>31f98761-4e09-4aa9-b656-e134cc8c4929.csv</t>
+          <t>2234b6eb-d6fb-46fc-ae5a-8116e1345c28.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>326cca1d-a499-4822-8d2f-55db856774d3</t>
+          <t>2c827641-7121-4f91-b9b6-8d643d7a16cc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPS USPSA July 2025</t>
+          <t>GPS USPSA November 2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jingyan "Coder" Wang</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.39%</t>
+          <t>50.68%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>455.7864</v>
+        <v>371.2574</v>
       </c>
       <c r="H9" t="n">
-        <v>135.95</v>
+        <v>150.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>73.39%</t>
+          <t>74.71%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1163,7 +1147,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1178,47 +1162,49 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="P9" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>326cca1d-a499-4822-8d2f-55db856774d3.csv</t>
+          <t>2c827641-7121-4f91-b9b6-8d643d7a16cc.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>356a42c1-7566-4dc8-a116-e2a6e28af842</t>
+          <t>2df6136a-9469-480b-a2c6-e45719ab0472</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 09MAY2026</t>
+          <t>GPS USPSA November Extra Saturday 2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1227,18 +1213,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.13%</t>
+          <t>61.48%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>633.3996</v>
+        <v>452.7645</v>
       </c>
       <c r="H10" t="n">
-        <v>135.99</v>
+        <v>147.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>98.93%</t>
+          <t>80.04%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1263,47 +1249,47 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="P10" t="n">
         <v>47</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>356a42c1-7566-4dc8-a116-e2a6e28af842.csv</t>
+          <t>2df6136a-9469-480b-a2c6-e45719ab0472.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3e93ea37-79a8-457c-9c13-a1c21e759c6f</t>
+          <t>31f98761-4e09-4aa9-b656-e134cc8c4929</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 8NOV2025</t>
+          <t>GPS USPSA August 2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1312,18 +1298,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.39%</t>
+          <t>56.32%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>532.9675</v>
+        <v>398.7853</v>
       </c>
       <c r="H11" t="n">
-        <v>129.52</v>
+        <v>159.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>96.80%</t>
+          <t>85.67%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1348,65 +1334,61 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3e93ea37-79a8-457c-9c13-a1c21e759c6f.csv</t>
+          <t>31f98761-4e09-4aa9-b656-e134cc8c4929.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4d125dd4-ba6d-4e02-9c75-e7f3d0fbe914</t>
+          <t>326cca1d-a499-4822-8d2f-55db856774d3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wallis Orchard June 2026 USPSA Match</t>
+          <t>GPS USPSA July 2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Jingyan "Coder" Wang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.81%</t>
+          <t>61.39%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>501.565</v>
+        <v>455.7864</v>
       </c>
       <c r="H12" t="n">
-        <v>130.39</v>
+        <v>135.95</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>82.04%</t>
+          <t>73.39%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1416,7 +1398,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1427,49 +1409,51 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="P12" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4d125dd4-ba6d-4e02-9c75-e7f3d0fbe914.csv</t>
+          <t>326cca1d-a499-4822-8d2f-55db856774d3.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4f1b4d5c-4da4-4fcf-8d7a-30514ee0676c</t>
+          <t>356a42c1-7566-4dc8-a116-e2a6e28af842</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 21FEB2026</t>
+          <t>Thunder Tactical Shooters USPSA Match 09MAY2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1478,18 +1462,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>66.83%</t>
+          <t>71.13%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>515.7404</v>
+        <v>633.3996</v>
       </c>
       <c r="H13" t="n">
-        <v>124.45</v>
+        <v>135.99</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>66.84%</t>
+          <t>98.93%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1514,45 +1498,47 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="P13" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4f1b4d5c-4da4-4fcf-8d7a-30514ee0676c.csv</t>
+          <t>356a42c1-7566-4dc8-a116-e2a6e28af842.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>513989aa-935c-467e-8c82-4019eb686fe1</t>
+          <t>3e93ea37-79a8-457c-9c13-a1c21e759c6f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TSV USPSA SATURDAY Pistol/PCC Match 9-19-2026</t>
+          <t>Thunder Tactical Shooters USPSA Match 8NOV2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1561,18 +1547,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>89.76%</t>
+          <t>69.39%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>611.6239</v>
+        <v>532.9675</v>
       </c>
       <c r="H14" t="n">
-        <v>125.97</v>
+        <v>129.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>81.01%</t>
+          <t>96.80%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1582,7 +1568,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1597,63 +1583,65 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>513989aa-935c-467e-8c82-4019eb686fe1.csv</t>
+          <t>3e93ea37-79a8-457c-9c13-a1c21e759c6f.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c</t>
+          <t>4587e22f-0f53-4b2d-abc7-b75a2abd48d4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 19JUL2025</t>
+          <t>Brazosland Pistoleros USPSA - Sunday March 15th</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jingyan "Coder PCC" Wang</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50.37%</t>
+          <t>47.89%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>350.8294</v>
+        <v>292.8761</v>
       </c>
       <c r="H15" t="n">
-        <v>143.02</v>
+        <v>116.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>57.33%</t>
+          <t>46.12%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1663,7 +1651,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1678,72 +1666,74 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P15" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c.csv</t>
+          <t>4587e22f-0f53-4b2d-abc7-b75a2abd48d4.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c</t>
+          <t>4d125dd4-ba6d-4e02-9c75-e7f3d0fbe914</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 19JUL2025</t>
+          <t>Wallis Orchard June 2026 USPSA Match</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jingyan "Coder Limited" Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.21%</t>
+          <t>67.81%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>266.1308</v>
+        <v>501.565</v>
       </c>
       <c r="H16" t="n">
-        <v>208.49</v>
+        <v>130.39</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.06%</t>
+          <t>82.04%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1759,71 +1749,69 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>A170259</t>
+          <t>A178525</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c.csv</t>
+          <t>4d125dd4-ba6d-4e02-9c75-e7f3d0fbe914.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>61cfe20d-c73d-4519-ad84-d0639b89b36f</t>
+          <t>4f1b4d5c-4da4-4fcf-8d7a-30514ee0676c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baps USPSA June 2025</t>
+          <t>Thunder Tactical Shooters USPSA Match 21FEB2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wang Jingyan</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.20%</t>
+          <t>66.83%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>257.1987</v>
+        <v>515.7404</v>
       </c>
       <c r="H17" t="n">
-        <v>189.49</v>
+        <v>124.45</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>41.71%</t>
+          <t>66.84%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1833,7 +1821,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1842,18 +1830,22 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P17" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
         <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -1861,28 +1853,28 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>61cfe20d-c73d-4519-ad84-d0639b89b36f.csv</t>
+          <t>4f1b4d5c-4da4-4fcf-8d7a-30514ee0676c.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>61e54a53-8bd5-4aa8-a89d-dc75842a3a89</t>
+          <t>50105bef-d748-459a-80b9-2fd9f5dc8cf5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bayou City Monthly June 14th at Oilfield Sports Complex</t>
+          <t>Kidlat Shooters December USPSA Match 12-6-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1891,18 +1883,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.70%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>346.2055</v>
-      </c>
-      <c r="H18" t="n">
-        <v>98.84</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63.61%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1912,7 +1902,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1926,68 +1916,58 @@
           <t>A170259</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>76</v>
-      </c>
-      <c r="P18" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>61e54a53-8bd5-4aa8-a89d-dc75842a3a89.csv</t>
+          <t>50105bef-d748-459a-80b9-2fd9f5dc8cf5.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc</t>
+          <t>513989aa-935c-467e-8c82-4019eb686fe1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 13SEP2025</t>
+          <t>TSV USPSA SATURDAY Pistol/PCC Match 9-19-2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coder PCC Wang</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.99%</t>
+          <t>89.76%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>418.4268</v>
+        <v>611.6239</v>
       </c>
       <c r="H19" t="n">
-        <v>114.06</v>
+        <v>125.97</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.45%</t>
+          <t>81.01%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1997,7 +1977,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2012,72 +1992,68 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="P19" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc.csv</t>
+          <t>513989aa-935c-467e-8c82-4019eb686fe1.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc</t>
+          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 13SEP2025</t>
+          <t>Thunder Tactical Shooters USPSA Match 19JUL2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coder Limited Wang</t>
+          <t>Jingyan "Coder PCC" Wang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52.70%</t>
+          <t>50.37%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>355.6987</v>
+        <v>350.8294</v>
       </c>
       <c r="H20" t="n">
-        <v>148.77</v>
+        <v>143.02</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>92.82%</t>
+          <t>57.33%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2097,75 +2073,77 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="P20" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc.csv</t>
+          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>65e36cba-4856-4e5b-9e1c-6658aca7b997</t>
+          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TSV Conroe USPSA SATURDAY 08-22-26</t>
+          <t>Thunder Tactical Shooters USPSA Match 19JUL2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Jingyan "Coder Limited" Wang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>78.90%</t>
+          <t>38.21%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>473.4245</v>
+        <v>266.1308</v>
       </c>
       <c r="H21" t="n">
-        <v>121.89</v>
+        <v>208.49</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>80.95%</t>
+          <t>47.06%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2174,67 +2152,73 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="P21" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>65e36cba-4856-4e5b-9e1c-6658aca7b997.csv</t>
+          <t>60b3b8d2-56f8-4fab-8840-820b74f3b10c.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>65ecbe20-63e3-4d6c-b382-02faf68b3e22</t>
+          <t>61cfe20d-c73d-4519-ad84-d0639b89b36f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 9AUG2025</t>
+          <t>Baps USPSA June 2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jim Wang</t>
+          <t>Wang Jingyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.57%</t>
+          <t>38.20%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>416.1532</v>
+        <v>257.1987</v>
       </c>
       <c r="H22" t="n">
-        <v>135.3</v>
+        <v>189.49</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>68.10%</t>
+          <t>41.71%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2244,7 +2228,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2253,53 +2237,47 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>A170259</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="P22" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
         <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>65ecbe20-63e3-4d6c-b382-02faf68b3e22.csv</t>
+          <t>61cfe20d-c73d-4519-ad84-d0639b89b36f.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>66b034c8-b789-40ac-b01c-5084ad4f3773</t>
+          <t>61e54a53-8bd5-4aa8-a89d-dc75842a3a89</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bayou City Monthly October 12th at Oilfield Sports Complex</t>
+          <t>Bayou City Monthly June 14th at Oilfield Sports Complex</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2308,18 +2286,18 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.26%</t>
+          <t>56.70%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>368.8188</v>
+        <v>346.2055</v>
       </c>
       <c r="H23" t="n">
-        <v>82.78</v>
+        <v>98.84</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>81.16%</t>
+          <t>63.61%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2329,7 +2307,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2344,47 +2322,47 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>66b034c8-b789-40ac-b01c-5084ad4f3773.csv</t>
+          <t>61e54a53-8bd5-4aa8-a89d-dc75842a3a89.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6876bc8c-98c9-4785-a901-3132faee1b3c</t>
+          <t>62784cac-8636-4824-ade8-4273f1096b86</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPS USPSA February Extra Saturday 2026</t>
+          <t>TSV Conroe USPSA SATURDAY 09-26-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2393,18 +2371,18 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>52.49%</t>
+          <t>79.98%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>356.1431</v>
+        <v>529.5111000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>126.86</v>
+        <v>128.79</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>58.85%</t>
+          <t>72.54%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2414,7 +2392,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2432,64 +2410,60 @@
         <v>98</v>
       </c>
       <c r="P24" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>6876bc8c-98c9-4785-a901-3132faee1b3c.csv</t>
+          <t>62784cac-8636-4824-ade8-4273f1096b86.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>749da8ab-c36b-4692-9814-3fa28490f875</t>
+          <t>639f43b1-171f-47b6-8224-b7f62ec55f50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 11JUl2026</t>
+          <t>Kidlat Shooters October USPSA Match 10-4-25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Coder PCC Wang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>66.02%</t>
+          <t>49.05%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>381.136</v>
+        <v>354.1647</v>
       </c>
       <c r="H25" t="n">
-        <v>55.19</v>
+        <v>181.58</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>48.07%</t>
+          <t>46.91%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2499,7 +2473,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2510,77 +2484,79 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>749da8ab-c36b-4692-9814-3fa28490f875.csv</t>
+          <t>639f43b1-171f-47b6-8224-b7f62ec55f50.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7ab5f726-bc21-4b6d-a802-8e5f6baf7a9f</t>
+          <t>639f43b1-171f-47b6-8224-b7f62ec55f50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wallis Orchard July 2026 USPSA Match</t>
+          <t>Kidlat Shooters October USPSA Match 10-4-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Coder Limited Wang</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>68.49%</t>
+          <t>35.57%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>558.8352</v>
+        <v>256.8312</v>
       </c>
       <c r="H26" t="n">
-        <v>121.19</v>
+        <v>175.32</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>90.75%</t>
+          <t>34.02%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2591,162 +2567,166 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="P26" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="Q26" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" t="n">
         <v>7</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>10</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>7ab5f726-bc21-4b6d-a802-8e5f6baf7a9f.csv</t>
+          <t>639f43b1-171f-47b6-8224-b7f62ec55f50.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7bc586f4-6cb5-421d-b2e4-f05147e10e98</t>
+          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPS USPSA Extra Saturday May 2025</t>
+          <t>Thunder Tactical Shooters USPSA Match 13SEP2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jingyan Wang</t>
+          <t>Coder PCC Wang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15.68%</t>
+          <t>61.99%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>117.5393</v>
+        <v>418.4268</v>
       </c>
       <c r="H27" t="n">
-        <v>379.94</v>
+        <v>114.06</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19.74%</t>
+          <t>76.45%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Carry Optics</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
       <c r="O27" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="P27" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="n">
-        <v>8</v>
-      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>7bc586f4-6cb5-421d-b2e4-f05147e10e98.csv</t>
+          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8a32723c-8885-48bf-afcb-25ccce44b263</t>
+          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPS USPSA August Extra Saturday 2025</t>
+          <t>Thunder Tactical Shooters USPSA Match 13SEP2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder Limited Wang</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.25%</t>
+          <t>52.70%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>488.0622</v>
+        <v>355.6987</v>
       </c>
       <c r="H28" t="n">
-        <v>139.24</v>
+        <v>148.77</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>92.82%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2761,69 +2741,65 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="P28" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>8a32723c-8885-48bf-afcb-25ccce44b263.csv</t>
+          <t>6511dedf-e56e-490a-8192-ad7a5e3accfc.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8c47ab24-490e-4f8c-b55d-ae1b31e4bdef</t>
+          <t>65e36cba-4856-4e5b-9e1c-6658aca7b997</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Baps USPSA November 2025</t>
+          <t>TSV Conroe USPSA SATURDAY 08-22-26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wang Coder</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>57.14%</t>
+          <t>78.90%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>417.7235</v>
+        <v>473.4245</v>
       </c>
       <c r="H29" t="n">
-        <v>168.31</v>
+        <v>121.89</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>68.22%</t>
+          <t>80.95%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2833,7 +2809,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2842,73 +2818,67 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>A170259</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="P29" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>8c47ab24-490e-4f8c-b55d-ae1b31e4bdef.csv</t>
+          <t>65e36cba-4856-4e5b-9e1c-6658aca7b997.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8d8d093e-8f97-4253-9069-1b454f8808c6</t>
+          <t>65ecbe20-63e3-4d6c-b382-02faf68b3e22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPS USPSA August 2026</t>
+          <t>Thunder Tactical Shooters USPSA Match 9AUG2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Jim Wang</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>76.75%</t>
+          <t>62.57%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>574.5927</v>
+        <v>416.1532</v>
       </c>
       <c r="H30" t="n">
-        <v>101.02</v>
+        <v>135.3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>86.95%</t>
+          <t>68.10%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2918,7 +2888,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2929,49 +2899,51 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="P30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>8d8d093e-8f97-4253-9069-1b454f8808c6.csv</t>
+          <t>65ecbe20-63e3-4d6c-b382-02faf68b3e22.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>95dd9851-e3f9-4049-86eb-25820c658b5a</t>
+          <t>66b034c8-b789-40ac-b01c-5084ad4f3773</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Baps USPSA May 2026</t>
+          <t>Bayou City Monthly October 12th at Oilfield Sports Complex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2980,18 +2952,18 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.52%</t>
+          <t>70.26%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>488.6707</v>
+        <v>368.8188</v>
       </c>
       <c r="H31" t="n">
-        <v>135.15</v>
+        <v>82.78</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>87.52%</t>
+          <t>81.16%</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3001,7 +2973,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -3016,45 +2988,47 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="P31" t="n">
         <v>37</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>95dd9851-e3f9-4049-86eb-25820c658b5a.csv</t>
+          <t>66b034c8-b789-40ac-b01c-5084ad4f3773.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>96b43687-6e76-40ed-a04d-ffd70a7e88b0</t>
+          <t>6876bc8c-98c9-4785-a901-3132faee1b3c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wallis Orchard APRIL 2026 SATURDAY USPSA Match</t>
+          <t>GPS USPSA February Extra Saturday 2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3063,18 +3037,18 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.35%</t>
+          <t>52.49%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>528.1025</v>
+        <v>356.1431</v>
       </c>
       <c r="H32" t="n">
-        <v>122.72</v>
+        <v>126.86</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>85.28%</t>
+          <t>58.85%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3093,67 +3067,73 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
       <c r="O32" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="P32" t="n">
         <v>46</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>96b43687-6e76-40ed-a04d-ffd70a7e88b0.csv</t>
+          <t>6876bc8c-98c9-4785-a901-3132faee1b3c.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>985c2d00-368a-47c8-8129-9d6c45fdf6eb</t>
+          <t>749da8ab-c36b-4692-9814-3fa28490f875</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wallis Orchard Jan 2026USPSA Match</t>
+          <t>Thunder Tactical Shooters USPSA Match 11JUl2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>54.97%</t>
+          <t>66.02%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>469.1523</v>
+        <v>381.136</v>
       </c>
       <c r="H33" t="n">
-        <v>158.78</v>
+        <v>55.19</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>84.02%</t>
+          <t>48.07%</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3163,7 +3143,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -3174,81 +3154,77 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A170259</t>
+          <t>A178525</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="P33" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>985c2d00-368a-47c8-8129-9d6c45fdf6eb.csv</t>
+          <t>749da8ab-c36b-4692-9814-3fa28490f875.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9fbd38d6-6db0-4fdc-a841-5c28c9641f5d</t>
+          <t>7ab5f726-bc21-4b6d-a802-8e5f6baf7a9f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wallis Orchard Aug USPSA Match</t>
+          <t>Wallis Orchard July 2026 USPSA Match</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>42.76%</t>
+          <t>68.49%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>345.6861</v>
+        <v>558.8352</v>
       </c>
       <c r="H34" t="n">
-        <v>205.12</v>
+        <v>121.19</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>61.72%</t>
+          <t>90.75%</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3259,132 +3235,132 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A170259</t>
+          <t>A178525</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="P34" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>9fbd38d6-6db0-4fdc-a841-5c28c9641f5d.csv</t>
+          <t>7ab5f726-bc21-4b6d-a802-8e5f6baf7a9f.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a6476489-5d99-45fd-9525-ca9c6cc458eb</t>
+          <t>7bc586f4-6cb5-421d-b2e4-f05147e10e98</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bayou City Monthly February 8th at Oilfield Sports Complex</t>
+          <t>GPS USPSA Extra Saturday May 2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Jingyan Wang</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.17%</t>
+          <t>15.68%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>431.7633</v>
+        <v>117.5393</v>
       </c>
       <c r="H35" t="n">
-        <v>123.84</v>
+        <v>379.94</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>72.62%</t>
+          <t>19.74%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>Carry Optics</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>A170259</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P35" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>8</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>a6476489-5d99-45fd-9525-ca9c6cc458eb.csv</t>
+          <t>7bc586f4-6cb5-421d-b2e4-f05147e10e98.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ab6b420e-c0b8-40f6-b50a-ecbed95536a9</t>
+          <t>8a32723c-8885-48bf-afcb-25ccce44b263</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPS USPSA May 2026</t>
+          <t>GPS USPSA August Extra Saturday 2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3393,18 +3369,18 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>67.32%</t>
+          <t>65.25%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>443.6805</v>
+        <v>488.0622</v>
       </c>
       <c r="H36" t="n">
-        <v>97.48</v>
+        <v>139.24</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>76.62%</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3414,7 +3390,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3429,65 +3405,67 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="P36" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>ab6b420e-c0b8-40f6-b50a-ecbed95536a9.csv</t>
+          <t>8a32723c-8885-48bf-afcb-25ccce44b263.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ae234d4e-eb2e-45a4-806f-1a992c5c3342</t>
+          <t>8a66d331-ef80-4ba8-b137-15a657f40493</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Baps USPSA March 2026</t>
+          <t>Kidlat Shooters AUGUST USPSA match 08-01-26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.97%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>486.0514</v>
-      </c>
-      <c r="H37" t="n">
-        <v>136.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>82.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3497,7 +3475,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3508,69 +3486,61 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A170259</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>124</v>
-      </c>
-      <c r="P37" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>4</v>
-      </c>
+          <t>A178525</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>ae234d4e-eb2e-45a4-806f-1a992c5c3342.csv</t>
+          <t>8a66d331-ef80-4ba8-b137-15a657f40493.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b7042f0d-5786-45ea-aecc-d7557a985e32</t>
+          <t>8c47ab24-490e-4f8c-b55d-ae1b31e4bdef</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 11OCT2025</t>
+          <t>Baps USPSA November 2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Wang Coder</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.51%</t>
+          <t>57.14%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>418.1559</v>
+        <v>417.7235</v>
       </c>
       <c r="H38" t="n">
-        <v>106</v>
+        <v>168.31</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>75.32%</t>
+          <t>68.22%</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3595,65 +3565,67 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="P38" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>b7042f0d-5786-45ea-aecc-d7557a985e32.csv</t>
+          <t>8c47ab24-490e-4f8c-b55d-ae1b31e4bdef.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>b76b98dc-1430-4a56-9a5c-3d73f9f7704f</t>
+          <t>8d8d093e-8f97-4253-9069-1b454f8808c6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bayou City Monthly September 13th at Oilfield Sports Complex</t>
+          <t>GPS USPSA August 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coder Wang</t>
+          <t>Coder W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>73.28%</t>
+          <t>76.75%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>478.5946</v>
+        <v>574.5927</v>
       </c>
       <c r="H39" t="n">
-        <v>84.95</v>
+        <v>101.02</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70.38%</t>
+          <t>86.95%</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3674,69 +3646,69 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>A170259</t>
+          <t>A178525</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="P39" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>b76b98dc-1430-4a56-9a5c-3d73f9f7704f.csv</t>
+          <t>8d8d093e-8f97-4253-9069-1b454f8808c6.csv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bbdf9b39-f6b3-4ae1-b48c-124652d7faef</t>
+          <t>95dd9851-e3f9-4049-86eb-25820c658b5a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Thunder Tactical Shooters USPSA Match 13JUN2026</t>
+          <t>Baps USPSA May 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>38.61%</t>
+          <t>61.52%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>298.0272</v>
+        <v>488.6707</v>
       </c>
       <c r="H40" t="n">
-        <v>155.75</v>
+        <v>135.15</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>52.32%</t>
+          <t>87.52%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3746,7 +3718,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3757,71 +3729,69 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A178525</t>
+          <t>A170259</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="P40" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="n">
-        <v>3</v>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>bbdf9b39-f6b3-4ae1-b48c-124652d7faef.csv</t>
+          <t>95dd9851-e3f9-4049-86eb-25820c658b5a.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bff00c64-dc88-41dc-83b4-6085e754cd7e</t>
+          <t>96b43687-6e76-40ed-a04d-ffd70a7e88b0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPS USPSA Extra Saturday August 2026</t>
+          <t>Wallis Orchard APRIL 2026 SATURDAY USPSA Match</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coder W</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>77.44%</t>
+          <t>65.35%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>566.7723</v>
+        <v>528.1025</v>
       </c>
       <c r="H41" t="n">
-        <v>106.34</v>
+        <v>122.72</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>81.75%</t>
+          <t>85.28%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3831,7 +3801,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3840,22 +3810,18 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>A178525</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P41" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -3863,48 +3829,48 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>bff00c64-dc88-41dc-83b4-6085e754cd7e.csv</t>
+          <t>96b43687-6e76-40ed-a04d-ffd70a7e88b0.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>d367a2ad-b30f-4e6b-810a-7d6c365c3069</t>
+          <t>96eea3c5-e7a7-4a2c-9bee-9b6b4f5a836f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPS USPSA Extra Saturday June 2025</t>
+          <t>Brazosland Pistoleros USPSA - Sunday January 11th</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jingyan "Coder" Wang 3</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>35.95%</t>
+          <t>61.76%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>241.9189</v>
+        <v>413.3276</v>
       </c>
       <c r="H42" t="n">
-        <v>221.01</v>
+        <v>118.64</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>49.93%</t>
+          <t>60.34%</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3914,14 +3880,10 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>MINOR</t>
@@ -3933,69 +3895,67 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="P42" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="Q42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" t="n">
         <v>2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="n">
         <v>2</v>
       </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>d367a2ad-b30f-4e6b-810a-7d6c365c3069.csv</t>
+          <t>96eea3c5-e7a7-4a2c-9bee-9b6b4f5a836f.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>d55ecd57-d182-4894-8267-ebecbc8e956e</t>
+          <t>985c2d00-368a-47c8-8129-9d6c45fdf6eb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wallis Orchard June USPSA Match</t>
+          <t>Wallis Orchard Jan 2026USPSA Match</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jingyang Wang</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>42.51%</t>
+          <t>54.97%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>381.8923</v>
+        <v>469.1523</v>
       </c>
       <c r="H43" t="n">
-        <v>211.69</v>
+        <v>158.78</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>59.15%</t>
+          <t>84.02%</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4005,7 +3965,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -4020,45 +3980,47 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="P43" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
         <v>5</v>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>d55ecd57-d182-4894-8267-ebecbc8e956e.csv</t>
+          <t>985c2d00-368a-47c8-8129-9d6c45fdf6eb.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e8b1fe24-17af-4768-b03b-f2350d352da8</t>
+          <t>9fbd38d6-6db0-4fdc-a841-5c28c9641f5d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GPS USPSA May Extra Saturday 2026</t>
+          <t>Wallis Orchard Aug USPSA Match</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4067,28 +4029,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.54%</t>
+          <t>42.76%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>432.2681</v>
+        <v>345.6861</v>
       </c>
       <c r="H44" t="n">
-        <v>123.81</v>
+        <v>205.12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>63.80%</t>
+          <t>61.72%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -4103,16 +4065,16 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="P44" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -4120,48 +4082,48 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>e8b1fe24-17af-4768-b03b-f2350d352da8.csv</t>
+          <t>9fbd38d6-6db0-4fdc-a841-5c28c9641f5d.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f13d14f8-b354-4c97-95f5-7d90b3ba06f0</t>
+          <t>a6476489-5d99-45fd-9525-ca9c6cc458eb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wallis Orchard July USPSA Match</t>
+          <t>Bayou City Monthly February 8th at Oilfield Sports Complex</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jingyan "Coder" Wang</t>
+          <t>Coder Wang</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>54.78%</t>
+          <t>60.17%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>379.5086</v>
+        <v>431.7633</v>
       </c>
       <c r="H45" t="n">
-        <v>124.29</v>
+        <v>123.84</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>67.48%</t>
+          <t>72.62%</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4171,7 +4133,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -4186,21 +4148,1365 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P45" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
-      </c>
-      <c r="R45" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
+          <t>a6476489-5d99-45fd-9525-ca9c6cc458eb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>a84bf20f-47c1-4900-bc8f-e51e2dcedc22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brazosland Pistoleros USPSA - Support for Kyle - Sunday July 13th</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>30</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Jingyan "Coder PCC" Wang</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.13%</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>289.6544</v>
+      </c>
+      <c r="H46" t="n">
+        <v>197.64</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>39.95%</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>102</v>
+      </c>
+      <c r="P46" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>6</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>a84bf20f-47c1-4900-bc8f-e51e2dcedc22.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>a84bf20f-47c1-4900-bc8f-e51e2dcedc22</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Brazosland Pistoleros USPSA - Support for Kyle - Sunday July 13th</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>36</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Jingyan "Coder Limited" Wang</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>28.76%</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>207.619</v>
+      </c>
+      <c r="H47" t="n">
+        <v>264.32</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>28.64%</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>99</v>
+      </c>
+      <c r="P47" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>a84bf20f-47c1-4900-bc8f-e51e2dcedc22.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ab6b420e-c0b8-40f6-b50a-ecbed95536a9</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GPS USPSA May 2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>38</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>67.32%</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>443.6805</v>
+      </c>
+      <c r="H48" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>76.62%</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>94</v>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>ab6b420e-c0b8-40f6-b50a-ecbed95536a9.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ae234d4e-eb2e-45a4-806f-1a992c5c3342</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Baps USPSA March 2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>24</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>62.97%</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>486.0514</v>
+      </c>
+      <c r="H49" t="n">
+        <v>136.17</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>82.63%</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>124</v>
+      </c>
+      <c r="P49" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>ae234d4e-eb2e-45a4-806f-1a992c5c3342.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>b7042f0d-5786-45ea-aecc-d7557a985e32</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Thunder Tactical Shooters USPSA Match 11OCT2025</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.51%</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>418.1559</v>
+      </c>
+      <c r="H50" t="n">
+        <v>106</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>75.32%</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>95</v>
+      </c>
+      <c r="P50" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>b7042f0d-5786-45ea-aecc-d7557a985e32.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>b76b98dc-1430-4a56-9a5c-3d73f9f7704f</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bayou City Monthly September 13th at Oilfield Sports Complex</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>73.28%</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>478.5946</v>
+      </c>
+      <c r="H51" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70.38%</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>96</v>
+      </c>
+      <c r="P51" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>b76b98dc-1430-4a56-9a5c-3d73f9f7704f.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bbdf9b39-f6b3-4ae1-b48c-124652d7faef</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Thunder Tactical Shooters USPSA Match 13JUN2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>82</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Coder W</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>38.61%</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>298.0272</v>
+      </c>
+      <c r="H52" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>52.32%</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>A178525</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>87</v>
+      </c>
+      <c r="P52" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>48</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>3</v>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>bbdf9b39-f6b3-4ae1-b48c-124652d7faef.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bff00c64-dc88-41dc-83b4-6085e754cd7e</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GPS USPSA Extra Saturday August 2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>23</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Coder W</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>77.44%</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>566.7723</v>
+      </c>
+      <c r="H53" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>81.75%</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>A178525</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>119</v>
+      </c>
+      <c r="P53" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>bff00c64-dc88-41dc-83b4-6085e754cd7e.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>c15bac7a-ca37-4beb-9847-944b42888440</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Brazosland Pistoleros USPSA CLASSIFIER Match - Sunday August 10th</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>39</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Coder PCC Wang</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>46.60%</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>202.7944</v>
+      </c>
+      <c r="H54" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>43.15%</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>64</v>
+      </c>
+      <c r="P54" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>c15bac7a-ca37-4beb-9847-944b42888440.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>c15bac7a-ca37-4beb-9847-944b42888440</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Brazosland Pistoleros USPSA CLASSIFIER Match - Sunday August 10th</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>45</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Coder Production Wang</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>39.53%</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>171.9956</v>
+      </c>
+      <c r="H55" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>36.59%</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>52</v>
+      </c>
+      <c r="P55" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>c15bac7a-ca37-4beb-9847-944b42888440.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>d0ef797f-7b47-4b4d-9f15-a80ee7064aa4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kidlat Shooters March USPSA Match 3-7-26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>23</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Coder Wang 4</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>62.93%</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>423.6553</v>
+      </c>
+      <c r="H56" t="n">
+        <v>141.65</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>55.02%</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>125</v>
+      </c>
+      <c r="P56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v>2</v>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>d0ef797f-7b47-4b4d-9f15-a80ee7064aa4.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>d367a2ad-b30f-4e6b-810a-7d6c365c3069</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GPS USPSA Extra Saturday June 2025</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>71</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Jingyan "Coder" Wang 3</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>35.95%</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>241.9189</v>
+      </c>
+      <c r="H57" t="n">
+        <v>221.01</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>49.93%</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>129</v>
+      </c>
+      <c r="P57" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>d367a2ad-b30f-4e6b-810a-7d6c365c3069.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>d55ecd57-d182-4894-8267-ebecbc8e956e</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Wallis Orchard June USPSA Match</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>77</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Jingyang Wang</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>42.51%</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>381.8923</v>
+      </c>
+      <c r="H58" t="n">
+        <v>211.69</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>59.15%</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>135</v>
+      </c>
+      <c r="P58" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>5</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>d55ecd57-d182-4894-8267-ebecbc8e956e.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>e80feea6-9382-4303-8d5a-a9f22302b263</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Brazosland Pistoleros USPSA- SUNDAY July 12th</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.01%</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>458.0725</v>
+      </c>
+      <c r="H59" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>67.86%</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>A178525</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>91</v>
+      </c>
+      <c r="P59" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>e80feea6-9382-4303-8d5a-a9f22302b263.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>e8b1fe24-17af-4768-b03b-f2350d352da8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GPS USPSA May Extra Saturday 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>43</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Coder Wang</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.54%</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>432.2681</v>
+      </c>
+      <c r="H60" t="n">
+        <v>123.81</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>63.80%</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>97</v>
+      </c>
+      <c r="P60" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>e8b1fe24-17af-4768-b03b-f2350d352da8.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>f13d14f8-b354-4c97-95f5-7d90b3ba06f0</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Wallis Orchard July USPSA Match</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>62</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Jingyan "Coder" Wang</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>54.78%</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>379.5086</v>
+      </c>
+      <c r="H61" t="n">
+        <v>124.29</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>67.48%</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PCC</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>A170259</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>99</v>
+      </c>
+      <c r="P61" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>3</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>f13d14f8-b354-4c97-95f5-7d90b3ba06f0.csv</t>
         </is>
       </c>
